--- a/data/trans_camb/P19-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 11,27</t>
+          <t>-0,0; 11,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,39; 19,74</t>
+          <t>6,69; 19,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 12,49</t>
+          <t>-4,87; 12,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 4,52</t>
+          <t>-9,59; 3,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 10,79</t>
+          <t>-3,33; 10,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 0,59</t>
+          <t>-15,87; 0,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 6,09</t>
+          <t>-2,86; 5,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 13,48</t>
+          <t>4,46; 13,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 3,5</t>
+          <t>-7,87; 4,66</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 49,64</t>
+          <t>-0,23; 50,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,02; 86,89</t>
+          <t>23,58; 84,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 54,62</t>
+          <t>-18,37; 57,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 11,65</t>
+          <t>-21,88; 9,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 29,06</t>
+          <t>-7,77; 27,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,96; 1,71</t>
+          <t>-37,46; 0,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 19,76</t>
+          <t>-8,28; 18,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,11; 45,67</t>
+          <t>12,84; 44,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-25,84; 11,34</t>
+          <t>-23,37; 14,84</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 7,46</t>
+          <t>-2,32; 7,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 13,52</t>
+          <t>2,9; 12,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 11,39</t>
+          <t>-2,74; 10,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 5,55</t>
+          <t>-4,87; 5,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 14,37</t>
+          <t>3,17; 14,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 4,13</t>
+          <t>-15,7; 4,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 4,56</t>
+          <t>-2,16; 5,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 12,42</t>
+          <t>4,53; 12,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 4,88</t>
+          <t>-7,49; 4,85</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 30,07</t>
+          <t>-7,95; 30,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,59; 54,08</t>
+          <t>9,66; 51,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 43,89</t>
+          <t>-8,98; 41,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 17,94</t>
+          <t>-13,27; 18,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,53; 47,38</t>
+          <t>8,41; 47,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,02; 12,93</t>
+          <t>-45,13; 12,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 16,15</t>
+          <t>-6,98; 19,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,46; 43,41</t>
+          <t>14,11; 43,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 16,57</t>
+          <t>-23,99; 16,92</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 4,98</t>
+          <t>-5,27; 4,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 7,41</t>
+          <t>-2,52; 7,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 7,08</t>
+          <t>-3,4; 7,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 6,53</t>
+          <t>-3,86; 6,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 8,41</t>
+          <t>-1,8; 8,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,18</t>
+          <t>1,5; 11,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 3,8</t>
+          <t>-3,26; 3,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 6,24</t>
+          <t>-1,04; 6,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 7,43</t>
+          <t>0,0; 7,28</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 20,68</t>
+          <t>-18,29; 20,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 31,58</t>
+          <t>-8,64; 31,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 29,74</t>
+          <t>-12,39; 31,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 21,08</t>
+          <t>-10,78; 20,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 28,28</t>
+          <t>-5,16; 27,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,43; 36,98</t>
+          <t>4,04; 36,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 13,81</t>
+          <t>-10,55; 13,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 22,7</t>
+          <t>-3,27; 21,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 26,65</t>
+          <t>-0,23; 26,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 4,14</t>
+          <t>-6,44; 4,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 8,2</t>
+          <t>-2,37; 9,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 4,03</t>
+          <t>-20,49; 4,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 0,85</t>
+          <t>-11,42; 0,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 4,72</t>
+          <t>-6,92; 4,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 10,88</t>
+          <t>-4,53; 11,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 1,17</t>
+          <t>-6,57; 1,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 4,35</t>
+          <t>-2,75; 4,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 3,71</t>
+          <t>-15,08; 4,06</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,29; 17,73</t>
+          <t>-21,56; 19,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 34,14</t>
+          <t>-7,71; 37,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,97; 15,57</t>
+          <t>-68,86; 15,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 2,48</t>
+          <t>-28,23; 1,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,09; 13,48</t>
+          <t>-17,07; 13,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 32,4</t>
+          <t>-11,44; 34,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,84; 4,11</t>
+          <t>-19,1; 3,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 14,29</t>
+          <t>-8,01; 16,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-45,73; 11,9</t>
+          <t>-45,24; 12,88</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 2,4</t>
+          <t>-9,5; 2,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 8,69</t>
+          <t>-3,19; 9,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 6,8</t>
+          <t>-4,59; 6,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 3,91</t>
+          <t>-8,82; 3,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 7,92</t>
+          <t>-5,1; 7,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 9,6</t>
+          <t>-0,86; 9,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 1,35</t>
+          <t>-7,43; 1,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 6,3</t>
+          <t>-2,85; 6,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 6,92</t>
+          <t>-0,95; 6,56</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-35,69; 10,71</t>
+          <t>-34,32; 11,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 42,73</t>
+          <t>-12,04; 43,19</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 31,32</t>
+          <t>-16,21; 32,5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 14,28</t>
+          <t>-26,5; 14,29</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 30,46</t>
+          <t>-15,61; 29,93</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 36,44</t>
+          <t>-3,1; 37,37</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-24,82; 5,36</t>
+          <t>-25,0; 6,64</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 25,13</t>
+          <t>-9,36; 24,92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 27,73</t>
+          <t>-3,15; 27,02</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 3,39</t>
+          <t>-9,3; 3,31</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 4,99</t>
+          <t>-7,45; 5,04</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 10,98</t>
+          <t>-0,63; 10,81</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 11,65</t>
+          <t>-1,87; 11,33</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,59; 14,37</t>
+          <t>2,16; 14,94</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 5,68</t>
+          <t>-17,71; 5,73</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 5,59</t>
+          <t>-3,59; 5,69</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 8,29</t>
+          <t>-0,82; 8,51</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 6,26</t>
+          <t>-12,39; 5,91</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 18,78</t>
+          <t>-39,45; 18,97</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-32,01; 27,31</t>
+          <t>-30,4; 28,1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 61,9</t>
+          <t>-2,48; 61,09</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 61,18</t>
+          <t>-7,55; 58,31</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5,89; 76,41</t>
+          <t>8,62; 83,29</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-65,5; 26,94</t>
+          <t>-67,53; 28,36</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 29,0</t>
+          <t>-15,21; 28,88</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 41,57</t>
+          <t>-3,69; 43,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-50,78; 31,27</t>
+          <t>-50,78; 29,61</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 1,2</t>
+          <t>-10,05; 1,42</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 6,17</t>
+          <t>-5,77; 5,79</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 6,43</t>
+          <t>-5,05; 6,81</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 4,35</t>
+          <t>-6,39; 4,5</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 9,77</t>
+          <t>-2,04; 9,56</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 4,38</t>
+          <t>-5,85; 4,25</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 1,34</t>
+          <t>-6,38; 1,3</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 6,43</t>
+          <t>-2,25; 6,4</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 4,18</t>
+          <t>-2,91; 4,07</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-60,4; 12,21</t>
+          <t>-62,38; 13,79</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,13; 63,77</t>
+          <t>-34,33; 58,13</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 62,32</t>
+          <t>-28,96; 69,32</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-38,52; 38,1</t>
+          <t>-36,97; 41,77</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 89,12</t>
+          <t>-12,97; 88,31</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-31,09; 40,53</t>
+          <t>-31,39; 40,7</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-40,81; 11,3</t>
+          <t>-40,82; 11,81</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 53,25</t>
+          <t>-14,56; 56,99</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 36,41</t>
+          <t>-18,16; 34,88</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,0</t>
+          <t>-2,31; 2,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,63</t>
+          <t>2,09; 6,41</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 3,23</t>
+          <t>-5,32; 3,2</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 1,4</t>
+          <t>-3,33; 1,24</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,43</t>
+          <t>0,88; 5,43</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 1,87</t>
+          <t>-7,14; 1,68</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,12</t>
+          <t>-2,06; 0,96</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,35</t>
+          <t>2,07; 5,26</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,62</t>
+          <t>-4,41; 1,67</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 8,5</t>
+          <t>-9,0; 8,38</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>7,74; 27,76</t>
+          <t>7,97; 26,84</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 13,16</t>
+          <t>-20,55; 13,1</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 4,68</t>
+          <t>-10,3; 4,17</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,79; 18,19</t>
+          <t>2,66; 18,04</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 6,12</t>
+          <t>-22,18; 5,39</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 4,08</t>
+          <t>-7,12; 3,46</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>6,48; 19,46</t>
+          <t>7,11; 19,09</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 5,82</t>
+          <t>-15,29; 6,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,25</t>
+          <t>2,48</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-7,85</t>
+          <t>-9,09</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,34</t>
+          <t>-3,2</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 11,5</t>
+          <t>-0,22; 11,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,69; 19,28</t>
+          <t>7,77; 20,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 12,68</t>
+          <t>-5,28; 11,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 3,58</t>
+          <t>-8,41; 4,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 10,09</t>
+          <t>-3,3; 10,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 0,31</t>
+          <t>-16,53; -0,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 5,64</t>
+          <t>-2,93; 5,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 13,78</t>
+          <t>4,22; 13,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 4,66</t>
+          <t>-8,46; 2,41</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-19,49%</t>
+          <t>-22,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-7,23%</t>
+          <t>-9,88%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 50,62</t>
+          <t>-1,15; 50,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,58; 84,95</t>
+          <t>28,03; 91,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 57,28</t>
+          <t>-19,2; 48,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,88; 9,48</t>
+          <t>-19,57; 12,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 27,29</t>
+          <t>-7,69; 28,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,46; 0,99</t>
+          <t>-39,5; -2,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 18,59</t>
+          <t>-8,66; 19,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,84; 44,69</t>
+          <t>12,29; 43,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-23,37; 14,84</t>
+          <t>-25,34; 7,99</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,76</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,7</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 7,35</t>
+          <t>-2,2; 7,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 12,71</t>
+          <t>2,88; 13,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 10,1</t>
+          <t>-5,04; 8,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 5,74</t>
+          <t>-5,43; 5,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 14,56</t>
+          <t>3,53; 14,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 4,02</t>
+          <t>-7,3; 5,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 5,31</t>
+          <t>-2,03; 5,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 12,5</t>
+          <t>4,95; 12,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 4,85</t>
+          <t>-3,79; 5,01</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-11,07%</t>
+          <t>-1,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 30,28</t>
+          <t>-7,53; 29,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,66; 51,07</t>
+          <t>9,69; 52,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 41,14</t>
+          <t>-18,1; 33,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 18,27</t>
+          <t>-15,09; 17,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,41; 47,75</t>
+          <t>9,8; 48,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 12,22</t>
+          <t>-20,06; 16,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 19,04</t>
+          <t>-6,45; 17,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,11; 43,6</t>
+          <t>15,62; 44,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,99; 16,92</t>
+          <t>-11,99; 17,59</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,07</t>
+          <t>5,15</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>2,66</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 4,83</t>
+          <t>-5,53; 4,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 7,19</t>
+          <t>-2,49; 7,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 7,37</t>
+          <t>-4,84; 5,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 6,13</t>
+          <t>-4,02; 5,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 8,23</t>
+          <t>-1,83; 8,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 11,03</t>
+          <t>0,55; 9,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 3,8</t>
+          <t>-3,07; 4,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 6,03</t>
+          <t>-0,91; 6,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,28</t>
+          <t>-0,7; 6,47</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,29; 20,62</t>
+          <t>-19,79; 19,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 31,58</t>
+          <t>-8,87; 33,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 31,42</t>
+          <t>-17,16; 23,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 20,09</t>
+          <t>-11,36; 19,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 27,31</t>
+          <t>-5,15; 27,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,04; 36,38</t>
+          <t>1,7; 32,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 13,5</t>
+          <t>-9,58; 14,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 21,46</t>
+          <t>-2,71; 21,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 26,14</t>
+          <t>-2,18; 23,12</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-5,75</t>
+          <t>2,05</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>-2,05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,09</t>
+          <t>0,08</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 4,8</t>
+          <t>-6,54; 4,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 9,09</t>
+          <t>-2,5; 8,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 4,18</t>
+          <t>-3,41; 7,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 0,48</t>
+          <t>-10,96; 1,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 4,53</t>
+          <t>-6,96; 4,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 11,64</t>
+          <t>-7,14; 2,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 1,07</t>
+          <t>-6,89; 1,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 4,9</t>
+          <t>-2,97; 4,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 4,06</t>
+          <t>-3,84; 3,49</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-21,13%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>-5,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-9,57%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 19,96</t>
+          <t>-21,81; 17,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 37,54</t>
+          <t>-8,51; 36,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-68,86; 15,83</t>
+          <t>-11,52; 30,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 1,47</t>
+          <t>-27,18; 4,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 13,62</t>
+          <t>-17,38; 14,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 34,06</t>
+          <t>-17,62; 8,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 3,67</t>
+          <t>-20,24; 2,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 16,35</t>
+          <t>-8,46; 16,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-45,24; 12,88</t>
+          <t>-11,12; 11,79</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,48</t>
+          <t>4,38</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>2,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 2,46</t>
+          <t>-10,12; 1,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 9,14</t>
+          <t>-3,11; 9,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 6,87</t>
+          <t>-4,21; 6,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 3,84</t>
+          <t>-8,83; 4,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 7,79</t>
+          <t>-4,4; 7,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 9,87</t>
+          <t>-1,11; 9,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 1,57</t>
+          <t>-7,22; 1,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 6,22</t>
+          <t>-2,46; 6,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 6,56</t>
+          <t>-0,68; 6,98</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 11,44</t>
+          <t>-36,69; 7,5</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 43,19</t>
+          <t>-11,68; 42,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 32,5</t>
+          <t>-14,4; 31,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 14,29</t>
+          <t>-26,92; 17,07</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 29,93</t>
+          <t>-13,43; 29,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 37,37</t>
+          <t>-3,82; 37,25</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 6,64</t>
+          <t>-24,5; 4,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 24,92</t>
+          <t>-8,4; 24,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 27,02</t>
+          <t>-2,17; 28,9</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5,4</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-4,6</t>
+          <t>4,35</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,83</t>
+          <t>4,83</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 3,31</t>
+          <t>-9,39; 3,47</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 5,04</t>
+          <t>-7,95; 4,22</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 10,81</t>
+          <t>-1,16; 11,71</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 11,33</t>
+          <t>-1,49; 11,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,16; 14,94</t>
+          <t>2,19; 15,13</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 5,73</t>
+          <t>-0,84; 9,13</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 5,69</t>
+          <t>-3,61; 5,67</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 8,51</t>
+          <t>-0,79; 8,53</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 5,91</t>
+          <t>1,08; 8,93</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-21,18%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-3,85%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-39,45; 18,97</t>
+          <t>-38,62; 20,16</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 28,1</t>
+          <t>-33,63; 23,33</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 61,09</t>
+          <t>-4,64; 65,97</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 58,31</t>
+          <t>-6,4; 60,58</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,62; 83,29</t>
+          <t>8,87; 80,9</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-67,53; 28,36</t>
+          <t>-3,32; 49,16</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 28,88</t>
+          <t>-15,43; 29,76</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 43,97</t>
+          <t>-3,04; 43,2</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-50,78; 29,61</t>
+          <t>4,49; 48,65</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>-0,0</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,73</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 1,42</t>
+          <t>-10,18; 1,04</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 5,79</t>
+          <t>-6,3; 5,85</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 6,81</t>
+          <t>-5,15; 6,81</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 4,5</t>
+          <t>-5,96; 4,41</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 9,56</t>
+          <t>-2,67; 9,43</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 4,25</t>
+          <t>-4,66; 4,59</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 1,3</t>
+          <t>-6,76; 1,26</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 6,4</t>
+          <t>-2,57; 6,53</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 4,07</t>
+          <t>-3,11; 4,49</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-0,77%</t>
+          <t>-0,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-62,38; 13,79</t>
+          <t>-60,42; 11,25</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-34,33; 58,13</t>
+          <t>-35,53; 60,42</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-28,96; 69,32</t>
+          <t>-29,83; 68,62</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-36,97; 41,77</t>
+          <t>-35,7; 41,02</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 88,31</t>
+          <t>-14,62; 89,93</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-31,39; 40,7</t>
+          <t>-27,44; 41,41</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-40,82; 11,81</t>
+          <t>-41,03; 11,83</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 56,99</t>
+          <t>-15,36; 59,02</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 34,88</t>
+          <t>-19,05; 39,89</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 2,0</t>
+          <t>-2,65; 2,03</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,41</t>
+          <t>1,81; 6,3</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 3,2</t>
+          <t>-1,09; 3,49</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 1,24</t>
+          <t>-3,16; 1,24</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,43</t>
+          <t>0,89; 5,37</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 1,68</t>
+          <t>-2,35; 1,83</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,96</t>
+          <t>-2,21; 0,98</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,26</t>
+          <t>2,01; 5,25</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 1,67</t>
+          <t>-0,81; 2,22</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-4,71%</t>
+          <t>-0,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 8,38</t>
+          <t>-10,05; 8,54</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>7,97; 26,84</t>
+          <t>7,02; 26,74</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-20,55; 13,1</t>
+          <t>-4,2; 14,61</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 4,17</t>
+          <t>-9,7; 4,04</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,66; 18,04</t>
+          <t>2,66; 17,83</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-22,18; 5,39</t>
+          <t>-7,18; 6,03</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 3,46</t>
+          <t>-7,69; 3,5</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>7,11; 19,09</t>
+          <t>6,82; 19,04</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 6,12</t>
+          <t>-2,77; 8,14</t>
         </is>
       </c>
     </row>
